--- a/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_2_Trade_data.xlsx
+++ b/RiskHalo_Certification_Challenge/data/Weekly_Trade_Data_Uploads/Week_2_Trade_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOFTWARES\CodeRepo\AIE9_CERTIFICATION_CHALLENGE\RiskHalo_Certification_Challenge\data\Weekly_Trade_Data_Uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD2B300-74C7-44AA-8CEE-112F6A26848F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9C5834-1B4E-4B63-8319-6F9923F70384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>Sr.</t>
   </si>
@@ -55,40 +55,67 @@
     <t>Turnover</t>
   </si>
   <si>
-    <t>OPT AXISBANK 24 Apr 2025 1100 CE</t>
-  </si>
-  <si>
-    <t>15-04-2025</t>
-  </si>
-  <si>
-    <t>OPT AXISBANK 24 Apr 2025 1130 PE</t>
-  </si>
-  <si>
-    <t>16-04-2025</t>
-  </si>
-  <si>
-    <t>OPT KOTAKBANK 24 Apr 2025 2120 CE</t>
-  </si>
-  <si>
-    <t>OPT CYIENT 24 Apr 2025 1160 PE</t>
-  </si>
-  <si>
-    <t>17-04-2025</t>
-  </si>
-  <si>
-    <t>OPT DELHIVERY 24 Apr 2025 270 CE</t>
+    <t>OPT DIVISLAB 29 May 2025 6450 CE</t>
+  </si>
+  <si>
+    <t>19-05-2025</t>
+  </si>
+  <si>
+    <t>OPT DELHIVERY 29 May 2025 340 CE</t>
+  </si>
+  <si>
+    <t>OPT COALINDIA 29 May 2025 400 CE</t>
+  </si>
+  <si>
+    <t>20-05-2025</t>
+  </si>
+  <si>
+    <t>OPT TATASTEEL 29 May 2025 160 CE</t>
+  </si>
+  <si>
+    <t>OPT DELHIVERY 29 May 2025 340 PE</t>
+  </si>
+  <si>
+    <t>21-05-2025</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 29 May 2025 24850 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 29 May 2025 24900 CE</t>
+  </si>
+  <si>
+    <t>OPT JIOFIN 29 May 2025 270 CE</t>
+  </si>
+  <si>
+    <t>OPT POLYCAB 29 May 2025 6000 CE</t>
+  </si>
+  <si>
+    <t>22-05-2025</t>
+  </si>
+  <si>
+    <t>OPT IREDA 29 May 2025 170 CE</t>
+  </si>
+  <si>
+    <t>23-05-2025</t>
+  </si>
+  <si>
+    <t>OPT DELHIVERY 29 May 2025 355 CE</t>
+  </si>
+  <si>
+    <t>OPT NIFTY 29 May 2025 24700 CE</t>
   </si>
   <si>
     <t>Buy Qty</t>
   </si>
   <si>
+    <t>Sell Qty</t>
+  </si>
+  <si>
+    <t>Avg Sell Price</t>
+  </si>
+  <si>
     <t>Avg Buy Price</t>
-  </si>
-  <si>
-    <t>Sell Qty</t>
-  </si>
-  <si>
-    <t>Avg Sell Price</t>
   </si>
 </sst>
 </file>
@@ -429,12 +456,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.140625" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1"/>
+    <col min="8" max="8" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -448,10 +476,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -460,10 +488,10 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
         <v>5</v>
@@ -486,237 +514,566 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="1">
-        <v>45762</v>
+        <v>45796</v>
       </c>
       <c r="D2">
-        <v>625</v>
+        <v>100</v>
       </c>
       <c r="E2">
-        <v>23.1</v>
+        <v>182.2</v>
       </c>
       <c r="F2">
-        <v>14437.5</v>
+        <v>18220</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H2">
-        <v>625</v>
+        <v>100</v>
       </c>
       <c r="I2">
-        <v>22.15</v>
+        <v>167</v>
       </c>
       <c r="J2">
-        <v>13843.75</v>
+        <v>16700</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>-593.75</v>
+        <v>-1520</v>
       </c>
       <c r="M2">
-        <v>73.09</v>
+        <v>79.13</v>
       </c>
       <c r="N2">
-        <v>-666.84</v>
+        <v>-1599.13</v>
       </c>
       <c r="O2">
-        <v>593.75</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="1">
-        <v>45763</v>
+        <v>45796</v>
       </c>
       <c r="D3">
-        <v>625</v>
+        <v>1525</v>
       </c>
       <c r="E3">
-        <v>16.05</v>
+        <v>15.65</v>
       </c>
       <c r="F3">
-        <v>10031.25</v>
+        <v>23866.25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H3">
-        <v>625</v>
+        <v>1525</v>
       </c>
       <c r="I3">
-        <v>16.600000000000001</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="J3">
-        <v>10375</v>
+        <v>26153.75</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>343.75</v>
+        <v>2287.5</v>
       </c>
       <c r="M3">
-        <v>66.459999999999994</v>
+        <v>94.98</v>
       </c>
       <c r="N3">
-        <v>277.29000000000002</v>
+        <v>2192.52</v>
       </c>
       <c r="O3">
-        <v>343.75</v>
+        <v>2287.5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1">
+        <v>45797</v>
+      </c>
+      <c r="D4">
+        <v>1050</v>
+      </c>
+      <c r="E4">
+        <v>18.149999999999999</v>
+      </c>
+      <c r="F4">
+        <v>19057.5</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1">
-        <v>45763</v>
-      </c>
-      <c r="D4">
-        <v>400</v>
-      </c>
-      <c r="E4">
-        <v>30.2</v>
-      </c>
-      <c r="F4">
-        <v>12080</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="H4">
-        <v>400</v>
+        <v>1050</v>
       </c>
       <c r="I4">
-        <v>31.35</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="J4">
-        <v>12540</v>
+        <v>19792.5</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>460</v>
+        <v>735</v>
       </c>
       <c r="M4">
-        <v>70.88</v>
+        <v>83.89</v>
       </c>
       <c r="N4">
-        <v>389.12</v>
+        <v>651.11</v>
       </c>
       <c r="O4">
-        <v>460</v>
+        <v>735</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>69</v>
+        <v>272</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>45764</v>
+        <v>45797</v>
       </c>
       <c r="D5">
-        <v>300</v>
+        <v>5500</v>
       </c>
       <c r="E5">
-        <v>31.45</v>
+        <v>3.4</v>
       </c>
       <c r="F5">
-        <v>9435</v>
+        <v>18700</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H5">
-        <v>300</v>
+        <v>5500</v>
       </c>
       <c r="I5">
-        <v>31.8</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
-        <v>9540</v>
+        <v>20900</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>105</v>
+        <v>2200</v>
       </c>
       <c r="M5">
-        <v>65</v>
+        <v>85.49</v>
       </c>
       <c r="N5">
-        <v>40</v>
+        <v>2114.5100000000002</v>
       </c>
       <c r="O5">
-        <v>105</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="1">
-        <v>45764</v>
+        <v>45798</v>
       </c>
       <c r="D6">
         <v>1525</v>
       </c>
       <c r="E6">
-        <v>11.45</v>
+        <v>7.6</v>
       </c>
       <c r="F6">
-        <v>17461.25</v>
+        <v>11590</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6">
         <v>1525</v>
       </c>
       <c r="I6">
-        <v>10.050000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
-        <v>15326.25</v>
+        <v>10065</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>-2135</v>
+        <v>-1525</v>
       </c>
       <c r="M6">
-        <v>77.16</v>
+        <v>66.72</v>
       </c>
       <c r="N6">
-        <v>-2212.16</v>
+        <v>-1591.72</v>
       </c>
       <c r="O6">
-        <v>2135</v>
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>199</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>45798</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <v>317.83</v>
+      </c>
+      <c r="F7">
+        <v>47673.75</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7">
+        <v>150</v>
+      </c>
+      <c r="I7">
+        <v>323.75</v>
+      </c>
+      <c r="J7">
+        <v>48562.5</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>888.75</v>
+      </c>
+      <c r="M7">
+        <v>185.02</v>
+      </c>
+      <c r="N7">
+        <v>703.73</v>
+      </c>
+      <c r="O7">
+        <v>888.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>200</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1">
+        <v>45798</v>
+      </c>
+      <c r="D8">
+        <v>75</v>
+      </c>
+      <c r="E8">
+        <v>285</v>
+      </c>
+      <c r="F8">
+        <v>21375</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8">
+        <v>75</v>
+      </c>
+      <c r="I8">
+        <v>266.14999999999998</v>
+      </c>
+      <c r="J8">
+        <v>19961.25</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>-1413.75</v>
+      </c>
+      <c r="M8">
+        <v>85.18</v>
+      </c>
+      <c r="N8">
+        <v>-1498.93</v>
+      </c>
+      <c r="O8">
+        <v>1413.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>141</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45798</v>
+      </c>
+      <c r="D9">
+        <v>1650</v>
+      </c>
+      <c r="E9">
+        <v>6.75</v>
+      </c>
+      <c r="F9">
+        <v>11137.5</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9">
+        <v>1650</v>
+      </c>
+      <c r="I9">
+        <v>5.75</v>
+      </c>
+      <c r="J9">
+        <v>9487.5</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>-1650</v>
+      </c>
+      <c r="M9">
+        <v>65.69</v>
+      </c>
+      <c r="N9">
+        <v>-1715.69</v>
+      </c>
+      <c r="O9">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>236</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1">
+        <v>45799</v>
+      </c>
+      <c r="D10">
+        <v>125</v>
+      </c>
+      <c r="E10">
+        <v>115.85</v>
+      </c>
+      <c r="F10">
+        <v>14481.25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10">
+        <v>125</v>
+      </c>
+      <c r="I10">
+        <v>104.95</v>
+      </c>
+      <c r="J10">
+        <v>13118.75</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>-1362.5</v>
+      </c>
+      <c r="M10">
+        <v>71.81</v>
+      </c>
+      <c r="N10">
+        <v>-1434.31</v>
+      </c>
+      <c r="O10">
+        <v>1362.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>135</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1">
+        <v>45800</v>
+      </c>
+      <c r="D11">
+        <v>2900</v>
+      </c>
+      <c r="E11">
+        <v>4.2</v>
+      </c>
+      <c r="F11">
+        <v>12180</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11">
+        <v>2900</v>
+      </c>
+      <c r="I11">
+        <v>3.75</v>
+      </c>
+      <c r="J11">
+        <v>10875</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>-1305</v>
+      </c>
+      <c r="M11">
+        <v>68.14</v>
+      </c>
+      <c r="N11">
+        <v>-1373.14</v>
+      </c>
+      <c r="O11">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>45800</v>
+      </c>
+      <c r="D12">
+        <v>1525</v>
+      </c>
+      <c r="E12">
+        <v>7.65</v>
+      </c>
+      <c r="F12">
+        <v>11666.25</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12">
+        <v>1525</v>
+      </c>
+      <c r="I12">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="J12">
+        <v>14030</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>2363.75</v>
+      </c>
+      <c r="M12">
+        <v>72.38</v>
+      </c>
+      <c r="N12">
+        <v>2291.37</v>
+      </c>
+      <c r="O12">
+        <v>2363.75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>191</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>45800</v>
+      </c>
+      <c r="D13">
+        <v>75</v>
+      </c>
+      <c r="E13">
+        <v>280.25</v>
+      </c>
+      <c r="F13">
+        <v>21018.75</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13">
+        <v>75</v>
+      </c>
+      <c r="I13">
+        <v>306.7</v>
+      </c>
+      <c r="J13">
+        <v>23002.5</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>1983.75</v>
+      </c>
+      <c r="M13">
+        <v>89.07</v>
+      </c>
+      <c r="N13">
+        <v>1894.68</v>
+      </c>
+      <c r="O13">
+        <v>1983.75</v>
       </c>
     </row>
   </sheetData>
